--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ14"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137131845</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131847</v>
       </c>
       <c r="B3" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,48 +904,55 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137131841</v>
+        <v>137150989</v>
       </c>
       <c r="B4" t="n">
-        <v>79483</v>
+        <v>92128</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712151</v>
+        <v>712145</v>
       </c>
       <c r="R4" t="n">
-        <v>7196377</v>
+        <v>7196270</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,54 +979,45 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131841</t>
+          <t>https://artportalen.se/Sighting/137150989</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137131846</v>
+        <v>137150992</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +1025,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712127</v>
+        <v>712135</v>
       </c>
       <c r="R5" t="n">
-        <v>7196332</v>
+        <v>7196273</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1084,54 +1089,45 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131846</t>
+          <t>https://artportalen.se/Sighting/137150992</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137131848</v>
+        <v>137150998</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>83354</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,37 +1135,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712197</v>
+        <v>712143</v>
       </c>
       <c r="R6" t="n">
-        <v>7196293</v>
+        <v>7196292</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,76 +1199,67 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131848</t>
+          <t>https://artportalen.se/Sighting/137150998</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137131849</v>
+        <v>137131841</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>79485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1269,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712203</v>
+        <v>712151</v>
       </c>
       <c r="R7" t="n">
-        <v>7196305</v>
+        <v>7196377</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1314,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,54 +1340,61 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131849</t>
+          <t>https://artportalen.se/Sighting/137131841</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137131850</v>
+        <v>137149824</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>79485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712191</v>
+        <v>712166</v>
       </c>
       <c r="R8" t="n">
-        <v>7196270</v>
+        <v>7196390</v>
       </c>
       <c r="S8" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1420,19 +1421,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>15:40</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>rik förekomst</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,71 +1437,79 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131850</t>
+          <t>https://artportalen.se/Sighting/137149824</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137131853</v>
+        <v>137150706</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>79485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712156</v>
+        <v>712150</v>
       </c>
       <c r="R9" t="n">
-        <v>7196212</v>
+        <v>7196388</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1532,19 +1536,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:47</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:47</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,79 +1552,83 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131853</t>
+          <t>https://artportalen.se/Sighting/137150706</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137131844</v>
+        <v>137150754</v>
       </c>
       <c r="B10" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712124</v>
+        <v>712127</v>
       </c>
       <c r="R10" t="n">
-        <v>7196342</v>
+        <v>7196396</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1652,24 +1655,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>flera draperade träd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,79 +1671,79 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131844</t>
+          <t>https://artportalen.se/Sighting/137150754</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137131851</v>
+        <v>137150785</v>
       </c>
       <c r="B11" t="n">
-        <v>58008</v>
+        <v>79485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712190</v>
+        <v>712120</v>
       </c>
       <c r="R11" t="n">
-        <v>7196257</v>
+        <v>7196382</v>
       </c>
       <c r="S11" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,24 +1770,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Barksprätt spår</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,79 +1786,79 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131851</t>
+          <t>https://artportalen.se/Sighting/137150785</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137131852</v>
+        <v>137149804</v>
       </c>
       <c r="B12" t="n">
-        <v>58008</v>
+        <v>80494</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712176</v>
+        <v>712166</v>
       </c>
       <c r="R12" t="n">
-        <v>7196223</v>
+        <v>7196390</v>
       </c>
       <c r="S12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,24 +1885,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:44</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barksprätt spår</t>
+          <t>rikligt på en asp</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,33 +1901,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131852</t>
+          <t>https://artportalen.se/Sighting/137149804</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137131855</v>
+        <v>137131846</v>
       </c>
       <c r="B13" t="n">
-        <v>58008</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,45 +1936,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712181</v>
+        <v>712127</v>
       </c>
       <c r="R13" t="n">
-        <v>7196361</v>
+        <v>7196332</v>
       </c>
       <c r="S13" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2029,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2039,12 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,16 +2031,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131855</t>
+          <t>https://artportalen.se/Sighting/137131846</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137131854</v>
+        <v>137131848</v>
       </c>
       <c r="B14" t="n">
-        <v>58112</v>
+        <v>80600</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2087,21 +2048,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2111,13 +2072,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712150</v>
+        <v>712197</v>
       </c>
       <c r="R14" t="n">
-        <v>7196214</v>
+        <v>7196293</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2146,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2156,12 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Två stycken</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,6 +2142,1409 @@
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131848</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137131849</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>712203</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7196305</v>
+      </c>
+      <c r="S15" t="n">
+        <v>9</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131849</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137131850</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>712191</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7196270</v>
+      </c>
+      <c r="S16" t="n">
+        <v>24</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131850</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137131853</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>712156</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7196212</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131853</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137150820</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>712197</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7196306</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>på en jättegrov urgammal sälg</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150820</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137150983</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80600</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>712153</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7196211</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150983</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137150985</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80611</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>712153</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7196211</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150985</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137131844</v>
+      </c>
+      <c r="B21" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>712124</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7196342</v>
+      </c>
+      <c r="S21" t="n">
+        <v>8</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131844</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137131851</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>712190</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7196257</v>
+      </c>
+      <c r="S22" t="n">
+        <v>19</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131851</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137131852</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>712176</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7196223</v>
+      </c>
+      <c r="S23" t="n">
+        <v>32</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131852</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137131855</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>712181</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7196361</v>
+      </c>
+      <c r="S24" t="n">
+        <v>7</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131855</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137150789</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>712114</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7196303</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150789</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137131854</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>712150</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7196214</v>
+      </c>
+      <c r="S26" t="n">
+        <v>9</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Två stycken</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137131854</t>
         </is>
@@ -2206,6 +3565,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137131845</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131847</v>
       </c>
       <c r="B3" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137150989</v>
       </c>
       <c r="B4" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137150992</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137150998</v>
       </c>
       <c r="B6" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>137131841</v>
       </c>
       <c r="B7" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137149824</v>
       </c>
       <c r="B8" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1464,7 +1464,7 @@
         <v>137150706</v>
       </c>
       <c r="B9" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137150754</v>
       </c>
       <c r="B10" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         <v>137150785</v>
       </c>
       <c r="B11" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>137149804</v>
       </c>
       <c r="B12" t="n">
-        <v>80494</v>
+        <v>80497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>137131846</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>137131848</v>
       </c>
       <c r="B14" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>137131849</v>
       </c>
       <c r="B15" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2264,7 +2264,7 @@
         <v>137131850</v>
       </c>
       <c r="B16" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>137131853</v>
       </c>
       <c r="B17" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>137150820</v>
       </c>
       <c r="B18" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>137150983</v>
       </c>
       <c r="B19" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>137150985</v>
       </c>
       <c r="B20" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ26"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137131845</v>
+        <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>712122</v>
+        <v>712172</v>
       </c>
       <c r="R2" t="n">
-        <v>7196346</v>
+        <v>7196318</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,27 +775,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131845</t>
+          <t>https://artportalen.se/Sighting/137233961</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137131847</v>
+        <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>712146</v>
+        <v>712122</v>
       </c>
       <c r="R3" t="n">
-        <v>7196276</v>
+        <v>7196346</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,16 +898,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131847</t>
+          <t>https://artportalen.se/Sighting/137131845</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137150989</v>
+        <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,26 +933,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lillberget, Vb</t>
+          <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>712145</v>
+        <v>712146</v>
       </c>
       <c r="R4" t="n">
-        <v>7196270</v>
+        <v>7196276</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,45 +972,54 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150989</t>
+          <t>https://artportalen.se/Sighting/137131847</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137150992</v>
+        <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712135</v>
+        <v>712145</v>
       </c>
       <c r="R5" t="n">
-        <v>7196273</v>
+        <v>7196270</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,16 +1120,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150992</t>
+          <t>https://artportalen.se/Sighting/137150989</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137150998</v>
+        <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>83356</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1137,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1166,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712143</v>
+        <v>712135</v>
       </c>
       <c r="R6" t="n">
-        <v>7196292</v>
+        <v>7196273</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,54 +1230,61 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150998</t>
+          <t>https://artportalen.se/Sighting/137150992</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137131841</v>
+        <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>79488</v>
+        <v>83369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712151</v>
+        <v>712143</v>
       </c>
       <c r="R7" t="n">
-        <v>7196377</v>
+        <v>7196292</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1302,99 +1311,83 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131841</t>
+          <t>https://artportalen.se/Sighting/137150998</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137149824</v>
+        <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>79488</v>
+        <v>92106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712166</v>
+        <v>712162</v>
       </c>
       <c r="R8" t="n">
-        <v>7196390</v>
+        <v>7196325</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,14 +1414,19 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:31</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>rik förekomst</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,34 +1435,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149824</t>
+          <t>https://artportalen.se/Sighting/137233962</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137150706</v>
+        <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1490,26 +1487,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lillberget, Vb</t>
+          <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712150</v>
+        <v>712151</v>
       </c>
       <c r="R9" t="n">
-        <v>7196388</v>
+        <v>7196377</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,14 +1526,19 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1552,34 +1547,33 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150706</t>
+          <t>https://artportalen.se/Sighting/137131841</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137150754</v>
+        <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,11 +1604,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1622,10 +1612,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>712127</v>
+        <v>712166</v>
       </c>
       <c r="R10" t="n">
-        <v>7196396</v>
+        <v>7196390</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1652,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>flera draperade träd</t>
+          <t>rik förekomst</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1689,16 +1679,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150754</t>
+          <t>https://artportalen.se/Sighting/137149824</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137150785</v>
+        <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1737,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>712120</v>
+        <v>712150</v>
       </c>
       <c r="R11" t="n">
-        <v>7196382</v>
+        <v>7196388</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1804,38 +1794,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150785</t>
+          <t>https://artportalen.se/Sighting/137150706</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137149804</v>
+        <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>80497</v>
+        <v>79501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1844,7 +1834,11 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1852,10 +1846,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>712166</v>
+        <v>712127</v>
       </c>
       <c r="R12" t="n">
-        <v>7196390</v>
+        <v>7196396</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1886,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>rikligt på en asp</t>
+          <t>flera draperade träd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,54 +1913,61 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137149804</t>
+          <t>https://artportalen.se/Sighting/137150754</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137131846</v>
+        <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712127</v>
+        <v>712120</v>
       </c>
       <c r="R13" t="n">
-        <v>7196332</v>
+        <v>7196382</v>
       </c>
       <c r="S13" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1993,19 +1994,14 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:26</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2014,71 +2010,72 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131846</t>
+          <t>https://artportalen.se/Sighting/137150785</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>137131848</v>
+        <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712197</v>
+        <v>712163</v>
       </c>
       <c r="R14" t="n">
-        <v>7196293</v>
+        <v>7196384</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2107,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2132,65 +2129,65 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131848</t>
+          <t>https://artportalen.se/Sighting/137233956</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>137131849</v>
+        <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712203</v>
+        <v>712185</v>
       </c>
       <c r="R15" t="n">
-        <v>7196305</v>
+        <v>7196340</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2219,7 +2216,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2226,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,65 +2241,65 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131849</t>
+          <t>https://artportalen.se/Sighting/137233957</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>137131850</v>
+        <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712191</v>
+        <v>712190</v>
       </c>
       <c r="R16" t="n">
-        <v>7196270</v>
+        <v>7196339</v>
       </c>
       <c r="S16" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2328,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2338,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,62 +2353,62 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131850</t>
+          <t>https://artportalen.se/Sighting/137233960</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>137131853</v>
+        <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712156</v>
+        <v>712168</v>
       </c>
       <c r="R17" t="n">
-        <v>7196212</v>
+        <v>7196294</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2443,7 +2440,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2453,7 +2450,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,72 +2465,65 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131853</t>
+          <t>https://artportalen.se/Sighting/137233963</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>137150820</v>
+        <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>80603</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712197</v>
+        <v>712148</v>
       </c>
       <c r="R18" t="n">
-        <v>7196306</v>
+        <v>7196294</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2560,14 +2550,19 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>på en jättegrov urgammal sälg</t>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,56 +2571,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Mikael Hägg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150820</t>
+          <t>https://artportalen.se/Sighting/137233964</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>137150983</v>
+        <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80603</v>
+        <v>80510</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2642,10 +2636,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712153</v>
+        <v>712166</v>
       </c>
       <c r="R19" t="n">
-        <v>7196211</v>
+        <v>7196390</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2680,6 +2674,11 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>rikligt på en asp</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2704,61 +2703,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150983</t>
+          <t>https://artportalen.se/Sighting/137149804</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>137150985</v>
+        <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80614</v>
+        <v>80616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lillberget, Vb</t>
+          <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712153</v>
+        <v>712127</v>
       </c>
       <c r="R20" t="n">
-        <v>7196211</v>
+        <v>7196332</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2785,45 +2777,54 @@
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150985</t>
+          <t>https://artportalen.se/Sighting/137131846</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137131844</v>
+        <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,45 +2832,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712124</v>
+        <v>712197</v>
       </c>
       <c r="R21" t="n">
-        <v>7196342</v>
+        <v>7196293</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2898,7 +2891,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2908,12 +2901,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Födosök</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,16 +2927,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131844</t>
+          <t>https://artportalen.se/Sighting/137131848</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137131851</v>
+        <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2956,45 +2944,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>712190</v>
+        <v>712203</v>
       </c>
       <c r="R22" t="n">
-        <v>7196257</v>
+        <v>7196305</v>
       </c>
       <c r="S22" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3023,7 +3003,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3033,12 +3013,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:42</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3064,16 +3039,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131851</t>
+          <t>https://artportalen.se/Sighting/137131849</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>137131852</v>
+        <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3081,45 +3056,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>712176</v>
+        <v>712191</v>
       </c>
       <c r="R23" t="n">
-        <v>7196223</v>
+        <v>7196270</v>
       </c>
       <c r="S23" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3148,7 +3115,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3158,12 +3125,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Barksprätt spår</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3189,16 +3151,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131852</t>
+          <t>https://artportalen.se/Sighting/137131850</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>137131855</v>
+        <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3206,45 +3168,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Södra Storliden, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712181</v>
+        <v>712156</v>
       </c>
       <c r="R24" t="n">
-        <v>7196361</v>
+        <v>7196212</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3273,7 +3227,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3283,12 +3237,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Barksprätt</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3314,16 +3263,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137131855</t>
+          <t>https://artportalen.se/Sighting/137131853</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>137150789</v>
+        <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>80616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3331,31 +3280,30 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3363,10 +3311,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712114</v>
+        <v>712197</v>
       </c>
       <c r="R25" t="n">
-        <v>7196303</v>
+        <v>7196306</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3403,7 +3351,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>ringhack på tall</t>
+          <t>på en jättegrov urgammal sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3412,6 +3360,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3429,16 +3378,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137150789</t>
+          <t>https://artportalen.se/Sighting/137150820</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>137131854</v>
+        <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>58112</v>
+        <v>80616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3446,37 +3395,44 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Södra Storliden, Vb</t>
+          <t>Lillberget, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712150</v>
+        <v>712153</v>
       </c>
       <c r="R26" t="n">
-        <v>7196214</v>
+        <v>7196211</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3503,48 +3459,993 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:48</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Två stycken</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150983</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137150985</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80627</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>712153</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7196211</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150985</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137131844</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>712124</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7196342</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Födosök</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131844</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137131851</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>712190</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7196257</v>
+      </c>
+      <c r="S29" t="n">
+        <v>19</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131851</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137131852</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>712176</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7196223</v>
+      </c>
+      <c r="S30" t="n">
+        <v>32</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Barksprätt spår</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131852</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137131855</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>712181</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7196361</v>
+      </c>
+      <c r="S31" t="n">
+        <v>7</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Barksprätt</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137131855</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137150789</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>712114</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7196303</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137150789</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137233959</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58021</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lillberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>712185</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7196340</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bohål</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Mikael Hägg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137233959</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137131854</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58125</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Södra Storliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>712150</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7196214</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Två stycken</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tommy Boström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137131854</t>
         </is>
@@ -3577,6 +4478,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80510</v>
+        <v>80512</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3048,7 +3048,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         <v>137131844</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>137131851</v>
       </c>
       <c r="B29" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>137131852</v>
       </c>
       <c r="B30" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3982,7 +3982,7 @@
         <v>137131855</v>
       </c>
       <c r="B31" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>137150789</v>
       </c>
       <c r="B32" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>137233959</v>
       </c>
       <c r="B33" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4339,7 +4339,7 @@
         <v>137131854</v>
       </c>
       <c r="B34" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -1834,11 +1834,7 @@
           <t>bålar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -3635,11 +3631,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3760,11 +3752,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3885,11 +3873,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -4010,11 +3994,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -4135,11 +4115,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80512</v>
+        <v>80522</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137131844</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131851</v>
       </c>
       <c r="B29" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>137131852</v>
       </c>
       <c r="B30" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>137131855</v>
       </c>
       <c r="B31" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>137150789</v>
       </c>
       <c r="B32" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>137233959</v>
       </c>
       <c r="B33" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>137131854</v>
       </c>
       <c r="B34" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80522</v>
+        <v>80525</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137131844</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131851</v>
       </c>
       <c r="B29" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>137131852</v>
       </c>
       <c r="B30" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>137131855</v>
       </c>
       <c r="B31" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>137150789</v>
       </c>
       <c r="B32" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>137233959</v>
       </c>
       <c r="B33" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>137131854</v>
       </c>
       <c r="B34" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80525</v>
+        <v>80530</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137131844</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131851</v>
       </c>
       <c r="B29" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>137131852</v>
       </c>
       <c r="B30" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>137131855</v>
       </c>
       <c r="B31" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>137150789</v>
       </c>
       <c r="B32" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>137233959</v>
       </c>
       <c r="B33" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>137131854</v>
       </c>
       <c r="B34" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80530</v>
+        <v>80541</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80541</v>
+        <v>80542</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80542</v>
+        <v>80544</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 39398-2026 artfynd.xlsx
+++ b/artfynd/A 39398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137233961</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137131845</v>
       </c>
       <c r="B3" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137131847</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137150989</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>137150992</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137150998</v>
       </c>
       <c r="B7" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1349,7 +1349,7 @@
         <v>137233962</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>137131841</v>
       </c>
       <c r="B9" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>137149824</v>
       </c>
       <c r="B10" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>137150706</v>
       </c>
       <c r="B11" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137150754</v>
       </c>
       <c r="B12" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>137150785</v>
       </c>
       <c r="B13" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
         <v>137233956</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         <v>137233957</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>137233960</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>137233963</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>137233964</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>137149804</v>
       </c>
       <c r="B19" t="n">
-        <v>80544</v>
+        <v>80548</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>137131846</v>
       </c>
       <c r="B20" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2820,7 +2820,7 @@
         <v>137131848</v>
       </c>
       <c r="B21" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>137131849</v>
       </c>
       <c r="B22" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
         <v>137131850</v>
       </c>
       <c r="B23" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3156,7 +3156,7 @@
         <v>137131853</v>
       </c>
       <c r="B24" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>137150820</v>
       </c>
       <c r="B25" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>137150983</v>
       </c>
       <c r="B26" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>137150985</v>
       </c>
       <c r="B27" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         <v>137131844</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131851</v>
       </c>
       <c r="B29" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>137131852</v>
       </c>
       <c r="B30" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>137131855</v>
       </c>
       <c r="B31" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>137150789</v>
       </c>
       <c r="B32" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>137233959</v>
       </c>
       <c r="B33" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4315,7 +4315,7 @@
         <v>137131854</v>
       </c>
       <c r="B34" t="n">
-        <v>58139</v>
+        <v>58142</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
